--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 10/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 10/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -462,22 +462,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.44451</v>
+        <v>16.68482</v>
       </c>
       <c r="D2" t="n">
-        <v>16.42536</v>
+        <v>16.44212</v>
       </c>
       <c r="E2" t="n">
-        <v>16.63825</v>
+        <v>16.51083</v>
       </c>
       <c r="F2" t="n">
-        <v>41.98384</v>
+        <v>42.7008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05025</v>
+        <v>0.04925</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8228</v>
+        <v>1.81603</v>
       </c>
     </row>
     <row r="3">
@@ -487,22 +487,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.81225</v>
+        <v>16.82468</v>
       </c>
       <c r="D3" t="n">
-        <v>16.32929</v>
+        <v>16.53145</v>
       </c>
       <c r="E3" t="n">
-        <v>16.28446</v>
+        <v>16.606</v>
       </c>
       <c r="F3" t="n">
-        <v>41.81156</v>
+        <v>41.6574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05047</v>
+        <v>0.04958</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79592</v>
+        <v>1.80505</v>
       </c>
     </row>
     <row r="4">
@@ -512,22 +512,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.80206</v>
+        <v>16.64035</v>
       </c>
       <c r="D4" t="n">
-        <v>16.36971</v>
+        <v>16.47929</v>
       </c>
       <c r="E4" t="n">
-        <v>16.49376</v>
+        <v>16.54393</v>
       </c>
       <c r="F4" t="n">
-        <v>41.28573</v>
+        <v>42.63099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04988</v>
+        <v>0.05036</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81058</v>
+        <v>1.78449</v>
       </c>
     </row>
     <row r="5">
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.7867</v>
+        <v>16.76058</v>
       </c>
       <c r="D5" t="n">
-        <v>16.29347</v>
+        <v>16.47307</v>
       </c>
       <c r="E5" t="n">
-        <v>16.44853</v>
+        <v>16.71685</v>
       </c>
       <c r="F5" t="n">
-        <v>41.73929</v>
+        <v>42.19529</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04981</v>
+        <v>0.05059</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78909</v>
+        <v>1.78083</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.58456</v>
+        <v>16.79838</v>
       </c>
       <c r="D6" t="n">
-        <v>16.20393</v>
+        <v>16.06669</v>
       </c>
       <c r="E6" t="n">
-        <v>16.0917</v>
+        <v>16.75038</v>
       </c>
       <c r="F6" t="n">
-        <v>42.0326</v>
+        <v>42.98065</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04943</v>
+        <v>0.05031</v>
       </c>
       <c r="H6" t="n">
-        <v>1.74021</v>
+        <v>1.80165</v>
       </c>
     </row>
     <row r="7">
@@ -587,22 +587,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.43169</v>
+        <v>16.57568</v>
       </c>
       <c r="D7" t="n">
-        <v>16.0871</v>
+        <v>16.3926</v>
       </c>
       <c r="E7" t="n">
-        <v>16.65449</v>
+        <v>16.46211</v>
       </c>
       <c r="F7" t="n">
-        <v>42.39525</v>
+        <v>41.96602</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05025</v>
+        <v>0.05012</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81696</v>
+        <v>1.80792</v>
       </c>
     </row>
     <row r="8">
@@ -612,22 +612,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.56342</v>
+        <v>16.77466</v>
       </c>
       <c r="D8" t="n">
-        <v>16.7183</v>
+        <v>16.0353</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3425</v>
+        <v>16.19767</v>
       </c>
       <c r="F8" t="n">
-        <v>41.84735</v>
+        <v>42.29283</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05032</v>
+        <v>0.05014</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7583</v>
+        <v>1.8306</v>
       </c>
     </row>
     <row r="9">
@@ -637,22 +637,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.72266</v>
+        <v>16.49489</v>
       </c>
       <c r="D9" t="n">
-        <v>16.46117</v>
+        <v>16.42541</v>
       </c>
       <c r="E9" t="n">
-        <v>16.17467</v>
+        <v>16.4883</v>
       </c>
       <c r="F9" t="n">
-        <v>42.83891</v>
+        <v>42.22922</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05016</v>
+        <v>0.04995</v>
       </c>
       <c r="H9" t="n">
-        <v>1.78791</v>
+        <v>1.8313</v>
       </c>
     </row>
     <row r="10">
@@ -662,22 +662,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.45108</v>
+        <v>16.56686</v>
       </c>
       <c r="D10" t="n">
-        <v>16.29574</v>
+        <v>16.22776</v>
       </c>
       <c r="E10" t="n">
-        <v>16.98422</v>
+        <v>16.47727</v>
       </c>
       <c r="F10" t="n">
-        <v>40.81355</v>
+        <v>41.92728</v>
       </c>
       <c r="G10" t="n">
         <v>0.0495</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81612</v>
+        <v>1.79474</v>
       </c>
     </row>
   </sheetData>
